--- a/data/import_9.26_move_to_branch.xlsx
+++ b/data/import_9.26_move_to_branch.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ef57ed840098249/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C6AC2B9-0F64-4F4A-B50F-54A6CFE59E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="สินค้า" sheetId="1" r:id="rId4"/>
+    <sheet name="สินค้า" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>รหัสสินค้า</t>
   </si>
@@ -58,9 +80,6 @@
     <t>840213261092</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>VFF0026(BR/BK,M41)</t>
   </si>
   <si>
@@ -70,9 +89,6 @@
     <t>840213261108</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>VFF0026(BR/BK,M42)</t>
   </si>
   <si>
@@ -82,9 +98,6 @@
     <t>840213261115</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>VFF0026(BR/BK,M43)</t>
   </si>
   <si>
@@ -94,9 +107,6 @@
     <t>840213261122</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>VFF0026(BR/BK,M44)</t>
   </si>
   <si>
@@ -106,9 +116,6 @@
     <t>840213261139</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>VFF0026(BR/BK,M45)</t>
   </si>
   <si>
@@ -136,9 +143,6 @@
     <t>840213261160</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>VFF0031(BK/LI,M40)</t>
   </si>
   <si>
@@ -157,9 +161,6 @@
     <t>840213260514</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>VFF0031(BK/LI,M42)</t>
   </si>
   <si>
@@ -169,9 +170,6 @@
     <t>840213260521</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>VFF0031(BK/LI,M43)</t>
   </si>
   <si>
@@ -190,9 +188,6 @@
     <t>840213260545</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>VFF0031(BK/LI,M45)</t>
   </si>
   <si>
@@ -238,9 +233,6 @@
     <t>840213260682</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,M42)</t>
   </si>
   <si>
@@ -250,9 +242,6 @@
     <t>840213260699</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,M43)</t>
   </si>
   <si>
@@ -262,9 +251,6 @@
     <t>840213260705</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,M44)</t>
   </si>
   <si>
@@ -274,9 +260,6 @@
     <t>840213260712</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,M45)</t>
   </si>
   <si>
@@ -295,9 +278,6 @@
     <t>840213260736</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,M47)</t>
   </si>
   <si>
@@ -307,9 +287,6 @@
     <t>840213260743</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,W36)</t>
   </si>
   <si>
@@ -337,9 +314,6 @@
     <t>840213260798</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>VFF0031(IV/DL,W39)</t>
   </si>
   <si>
@@ -394,9 +368,6 @@
     <t>840213254339</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>VFF0031(TT/BK,M42)</t>
   </si>
   <si>
@@ -406,9 +377,6 @@
     <t>840213254346</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>VFF0031(TT/BK,M43)</t>
   </si>
   <si>
@@ -427,9 +395,6 @@
     <t>840213254360</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>VFF0031(TT/BK,M45)</t>
   </si>
   <si>
@@ -439,9 +404,6 @@
     <t>840213254377</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>VFF0031(TT/BK,M46)</t>
   </si>
   <si>
@@ -478,9 +440,6 @@
     <t>840213254438</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>VFF0031(TT/BK,W38)</t>
   </si>
   <si>
@@ -560,9 +519,6 @@
   </si>
   <si>
     <t>840213261290</t>
-  </si>
-  <si>
-    <t>16</t>
   </si>
   <si>
     <t>VFF0032(BR/BK,M43)</t>
@@ -613,42 +569,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[Blue]#,##0.00;[Red]\(#,##0.00\);[Black]0.00"/>
+    <numFmt numFmtId="187" formatCode="[Blue]#,##0.00;[Red]\(#,##0.00\);[Black]0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Tahoma"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -668,9 +627,21 @@
         <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -681,6 +652,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -695,8 +668,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -706,108 +681,117 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1005,21 +989,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln cap="flat" cmpd="sng" w="12700" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="19050" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln cap="flat" cmpd="sng" w="25400" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1036,7 +1020,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" rotWithShape="0" algn="ctr" dir="5400000" dist="19050">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1106,31 +1090,26 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}"/>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L100"/>
+  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.57"/>
-    <col customWidth="1" min="2" max="2" width="60.14"/>
-    <col customWidth="1" min="3" max="3" width="10.71"/>
-    <col customWidth="1" min="4" max="4" width="16.43"/>
-    <col customWidth="1" min="5" max="6" width="9.43"/>
-    <col customWidth="1" min="7" max="7" width="9.29"/>
-    <col customWidth="1" min="8" max="8" width="11.86"/>
-    <col customWidth="1" min="9" max="11" width="8.43"/>
-    <col customWidth="1" min="12" max="12" width="8.57"/>
+    <col min="1" max="1" width="27.59765625" customWidth="1"/>
+    <col min="2" max="2" width="60.09765625" customWidth="1"/>
+    <col min="3" max="3" width="10.69921875" customWidth="1"/>
+    <col min="4" max="4" width="16.3984375" customWidth="1"/>
+    <col min="5" max="6" width="9.3984375" customWidth="1"/>
+    <col min="7" max="7" width="9.296875" customWidth="1"/>
+    <col min="8" max="8" width="11.8984375" customWidth="1"/>
+    <col min="9" max="11" width="8.3984375" customWidth="1"/>
+    <col min="12" max="12" width="8.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
@@ -1176,2081 +1155,2144 @@
         <v>13</v>
       </c>
       <c r="C2" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F2" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
       <c r="K2" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="14">
+        <f>E2-F2-G2-H2-I2-J2-M2-K2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="E3" s="10">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F3" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="12"/>
       <c r="K3" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="14">
+        <f t="shared" ref="L3:L56" si="0">E3-F3-G3-H3-I3-J3-M3-K3</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="C4" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="10">
         <v>21</v>
       </c>
-      <c r="C4" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="10">
-        <v>21.0</v>
-      </c>
       <c r="F4" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
       <c r="K4" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="E5" s="10">
         <v>24</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="10">
-        <v>24.0</v>
-      </c>
       <c r="F5" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
       <c r="K5" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>1</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E6" s="10">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F6" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
       <c r="K6" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1</v>
+      </c>
+      <c r="L6" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C7" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E7" s="10">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F7" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
       <c r="K7" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1</v>
+      </c>
+      <c r="L7" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C8" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E8" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F8" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>1</v>
+      </c>
+      <c r="L8" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C9" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E9" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F9" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C10" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E10" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F10" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C11" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E11" s="10">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F11" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L11" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="10">
+        <v>30</v>
+      </c>
+      <c r="F12" s="11">
+        <v>2</v>
+      </c>
+      <c r="G12" s="11">
+        <v>2</v>
+      </c>
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11">
+        <v>1</v>
+      </c>
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="10">
+        <v>30</v>
+      </c>
+      <c r="F13" s="11">
+        <v>2</v>
+      </c>
+      <c r="G13" s="11">
+        <v>2</v>
+      </c>
+      <c r="H13" s="11">
+        <v>1</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C14" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E14" s="10">
+        <v>27</v>
+      </c>
+      <c r="F14" s="11">
+        <v>2</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11">
+        <v>1</v>
+      </c>
+      <c r="K14" s="13">
+        <v>1</v>
+      </c>
+      <c r="L14" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="10">
-        <v>30.0</v>
-      </c>
-      <c r="F12" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H12" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L12" s="14" t="s">
+      <c r="B15" s="7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="C15" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="10">
-        <v>30.0</v>
-      </c>
-      <c r="F13" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H13" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="10">
-        <v>27.0</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G14" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="H14" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="E15" s="10">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F15" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>1</v>
+      </c>
+      <c r="L15" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C16" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E16" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F16" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
       <c r="K16" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>1</v>
+      </c>
+      <c r="L16" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C17" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E17" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F17" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="15">
+        <v>27</v>
+      </c>
+      <c r="F18" s="12">
+        <v>2</v>
+      </c>
+      <c r="G18" s="12">
+        <v>1</v>
+      </c>
+      <c r="H18" s="12">
+        <v>1</v>
+      </c>
+      <c r="I18" s="18">
+        <v>1</v>
+      </c>
+      <c r="J18" s="18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="13">
+        <v>1</v>
+      </c>
+      <c r="L18" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="10">
+        <v>42</v>
+      </c>
+      <c r="F19" s="11">
+        <v>4</v>
+      </c>
+      <c r="G19" s="11">
+        <v>2</v>
+      </c>
+      <c r="H19" s="11">
+        <v>1</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1</v>
+      </c>
+      <c r="J19" s="11">
+        <v>1</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="10">
+        <v>51</v>
+      </c>
+      <c r="F20" s="11">
+        <v>4</v>
+      </c>
+      <c r="G20" s="11">
+        <v>2</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1</v>
+      </c>
+      <c r="I20" s="11">
+        <v>1</v>
+      </c>
+      <c r="J20" s="11">
+        <v>1</v>
+      </c>
+      <c r="K20" s="13">
+        <v>1</v>
+      </c>
+      <c r="L20" s="14">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B21" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C21" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="F18" s="12">
-        <v>2.0</v>
-      </c>
-      <c r="G18" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+      <c r="E21" s="10">
+        <v>48</v>
+      </c>
+      <c r="F21" s="11">
+        <v>4</v>
+      </c>
+      <c r="G21" s="11">
+        <v>2</v>
+      </c>
+      <c r="H21" s="11">
+        <v>1</v>
+      </c>
+      <c r="I21" s="11">
+        <v>1</v>
+      </c>
+      <c r="J21" s="11">
+        <v>1</v>
+      </c>
+      <c r="K21" s="13">
+        <v>1</v>
+      </c>
+      <c r="L21" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D19" s="9" t="s">
+      <c r="C22" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="10">
-        <v>42.0</v>
-      </c>
-      <c r="F19" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="G19" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H19" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I19" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="J19" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="K19" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L19" s="14" t="s">
+      <c r="E22" s="10">
+        <v>33</v>
+      </c>
+      <c r="F22" s="11">
+        <v>2</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11">
+        <v>1</v>
+      </c>
+      <c r="I22" s="11">
+        <v>1</v>
+      </c>
+      <c r="J22" s="11">
+        <v>1</v>
+      </c>
+      <c r="K22" s="13">
+        <v>1</v>
+      </c>
+      <c r="L22" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C23" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="E23" s="10">
+        <v>24</v>
+      </c>
+      <c r="F23" s="11">
+        <v>1</v>
+      </c>
+      <c r="G23" s="11">
+        <v>1</v>
+      </c>
+      <c r="H23" s="12">
+        <v>1</v>
+      </c>
+      <c r="I23" s="12">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="10">
-        <v>51.0</v>
-      </c>
-      <c r="F20" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="G20" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H20" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I20" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="J20" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="K20" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L20" s="14" t="s">
+      <c r="B24" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="7" t="s">
+      <c r="C24" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="10">
-        <v>48.0</v>
-      </c>
-      <c r="F21" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="G21" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H21" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I21" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="J21" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="K21" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="10">
-        <v>33.0</v>
-      </c>
-      <c r="F22" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G22" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I22" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="J22" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="K22" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="10">
-        <v>24.0</v>
-      </c>
-      <c r="F23" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="G23" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J23" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="K23" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>93</v>
-      </c>
       <c r="E24" s="10">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F24" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C25" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E25" s="10">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F25" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C26" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E26" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F26" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C27" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E27" s="10">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F27" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C28" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E28" s="10">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="F28" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C29" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E29" s="10">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="F29" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C30" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E30" s="10">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="F30" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L30" s="14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C31" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E31" s="10">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F31" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C32" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E32" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F32" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C33" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E33" s="10">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F33" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
       <c r="K33" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="10">
+        <v>27</v>
+      </c>
+      <c r="F34" s="11">
+        <v>2</v>
+      </c>
+      <c r="G34" s="11">
+        <v>1</v>
+      </c>
+      <c r="H34" s="11">
+        <v>1</v>
+      </c>
+      <c r="I34" s="11">
+        <v>1</v>
+      </c>
+      <c r="J34" s="11">
+        <v>1</v>
+      </c>
+      <c r="K34" s="13">
+        <v>1</v>
+      </c>
+      <c r="L34" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" s="10">
+        <v>39</v>
+      </c>
+      <c r="F35" s="11">
+        <v>2</v>
+      </c>
+      <c r="G35" s="11">
+        <v>2</v>
+      </c>
+      <c r="H35" s="12">
+        <v>1</v>
+      </c>
+      <c r="I35" s="12">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12">
+        <v>1</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="10">
+        <v>39</v>
+      </c>
+      <c r="F36" s="11">
+        <v>2</v>
+      </c>
+      <c r="G36" s="11">
+        <v>2</v>
+      </c>
+      <c r="H36" s="12">
+        <v>1</v>
+      </c>
+      <c r="I36" s="12">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12">
+        <v>1</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1</v>
+      </c>
+      <c r="L36" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="15">
+        <v>36</v>
+      </c>
+      <c r="F37" s="12">
+        <v>2</v>
+      </c>
+      <c r="G37" s="12">
+        <v>1</v>
+      </c>
+      <c r="H37" s="12">
+        <v>1</v>
+      </c>
+      <c r="I37" s="12">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12">
+        <v>1</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1</v>
+      </c>
+      <c r="L37" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E38" s="10">
+        <v>18</v>
+      </c>
+      <c r="F38" s="11">
+        <v>1</v>
+      </c>
+      <c r="G38" s="11">
+        <v>1</v>
+      </c>
+      <c r="H38" s="12">
+        <v>1</v>
+      </c>
+      <c r="I38" s="12">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12">
+        <v>1</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="C39" s="8">
+        <v>5980</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="10">
-        <v>27.0</v>
-      </c>
-      <c r="F34" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G34" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="H34" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="I34" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="J34" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="K34" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L34" s="14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" s="10">
-        <v>39.0</v>
-      </c>
-      <c r="F35" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G35" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H35" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I35" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J35" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="K35" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C36" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E36" s="10">
-        <v>39.0</v>
-      </c>
-      <c r="F36" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="G36" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="H36" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I36" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J36" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="K36" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L36" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C37" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="F37" s="12">
-        <v>2.0</v>
-      </c>
-      <c r="G37" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H37" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I37" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J37" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="K37" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E38" s="10">
-        <v>18.0</v>
-      </c>
-      <c r="F38" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="H38" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I38" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J38" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="K38" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L38" s="14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" s="8">
-        <v>5980.0</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="E39" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F39" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
       <c r="K39" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C40" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="E40" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F40" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
       <c r="K40" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C41" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="E41" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F41" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
       <c r="K41" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L41" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C42" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="E42" s="10">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F42" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
       <c r="K42" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L42" s="14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="C43" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="E43" s="10">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="F43" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K43" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L43" s="14" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C44" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="E44" s="10">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="F44" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L44" s="14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="C45" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="E45" s="10">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="F45" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L45" s="14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L45" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C46" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E46" s="10">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F46" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
       <c r="K46" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L46" s="14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C47" s="8">
-        <v>5980.0</v>
+        <v>5980</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="E47" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F47" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
       <c r="K47" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L47" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="C48" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="E48" s="10">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F48" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
       <c r="K48" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L48" s="14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C49" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="E49" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F49" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
       <c r="J49" s="11"/>
       <c r="K49" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L49" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C50" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="E50" s="10">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F50" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L50" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C51" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="E51" s="10">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="F51" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H51" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L51" s="14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="C52" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="E52" s="10">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="F52" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H52" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K52" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L52" s="14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="C53" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="E53" s="10">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="F53" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L53" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C54" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="E54" s="10">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F54" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="H54" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I54" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="J54" s="12">
-        <v>1.0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
       <c r="K54" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L54" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="C55" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E55" s="10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F55" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
       <c r="J55" s="12"/>
       <c r="K55" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L55" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="C56" s="8">
-        <v>7980.0</v>
+        <v>7980</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E56" s="10">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F56" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="11"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
       <c r="K56" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="L56" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="E57" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="L56" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E57" s="16">
         <f t="shared" ref="E57:L57" si="1">SUM(E2:E56)</f>
         <v>1068</v>
       </c>
-      <c r="F57" s="16" t="str">
+      <c r="F57" s="16">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="G57" s="16" t="str">
+      <c r="G57" s="16">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="H57" s="16" t="str">
+      <c r="H57" s="16">
         <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="I57" s="16" t="str">
+        <v>35</v>
+      </c>
+      <c r="I57" s="16">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="J57" s="16" t="str">
+        <v>24</v>
+      </c>
+      <c r="J57" s="16">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="K57" s="16" t="str">
+        <v>24</v>
+      </c>
+      <c r="K57" s="16">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="L57" s="16" t="str">
+      <c r="L57" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L58" s="17"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L59" s="17"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L60" s="17"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L61" s="17"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L62" s="17"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L63" s="17"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L64" s="17"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L65" s="17"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L66" s="17"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L67" s="17"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L68" s="17"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L69" s="17"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L70" s="17"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L71" s="17"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L72" s="17"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L73" s="17"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L74" s="17"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L75" s="17"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L76" s="17"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L77" s="17"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L78" s="17"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L79" s="17"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L80" s="17"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L81" s="17"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L82" s="17"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L83" s="17"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L84" s="17"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L85" s="17"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L86" s="17"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L87" s="17"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L88" s="17"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L89" s="17"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L90" s="17"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L91" s="17"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L92" s="17"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L93" s="17"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L94" s="17"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L95" s="17"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L96" s="17"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L97" s="17"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L98" s="17"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L99" s="17"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L100" s="17"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>